--- a/Excel Logic/KaKb Key Calculator Formulas.xlsx
+++ b/Excel Logic/KaKb Key Calculator Formulas.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkawagoe/Scripts/Lab Check/KaKb Lab/Excel Logic/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8D4FEAA-8DE7-A44D-8F34-A1E08645C2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585DD216-9E5E-6F44-8989-0A2ACDFF7491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="22580" xr2:uid="{A489C9C8-2BC1-984E-9DE9-D2012CFE6641}"/>
   </bookViews>
   <sheets>
     <sheet name="KaKb Key Calculator Formulas" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="55">
   <si>
     <t>Trial 1</t>
   </si>
@@ -182,283 +182,7 @@
     <t>Label</t>
   </si>
   <si>
-    <t>F5</t>
-  </si>
-  <si>
-    <t>F6</t>
-  </si>
-  <si>
-    <t>F7</t>
-  </si>
-  <si>
-    <t>F8</t>
-  </si>
-  <si>
-    <t>F9</t>
-  </si>
-  <si>
-    <t>F11</t>
-  </si>
-  <si>
-    <t>F12</t>
-  </si>
-  <si>
-    <t>F13</t>
-  </si>
-  <si>
-    <t>F14</t>
-  </si>
-  <si>
-    <t>F15</t>
-  </si>
-  <si>
-    <t>F17</t>
-  </si>
-  <si>
-    <t>F18</t>
-  </si>
-  <si>
-    <t>F19</t>
-  </si>
-  <si>
-    <t>F20</t>
-  </si>
-  <si>
-    <t>F21</t>
-  </si>
-  <si>
-    <t>F22</t>
-  </si>
-  <si>
-    <t>F23</t>
-  </si>
-  <si>
-    <t>F24</t>
-  </si>
-  <si>
-    <t>F27</t>
-  </si>
-  <si>
-    <t>F28</t>
-  </si>
-  <si>
-    <t>F29</t>
-  </si>
-  <si>
-    <t>F30</t>
-  </si>
-  <si>
-    <t>F31</t>
-  </si>
-  <si>
-    <t>F32</t>
-  </si>
-  <si>
-    <t>F34</t>
-  </si>
-  <si>
-    <t>F35</t>
-  </si>
-  <si>
-    <t>F36</t>
-  </si>
-  <si>
-    <t>F37</t>
-  </si>
-  <si>
-    <t>F38</t>
-  </si>
-  <si>
-    <t>F40</t>
-  </si>
-  <si>
-    <t>F41</t>
-  </si>
-  <si>
-    <t>F42</t>
-  </si>
-  <si>
-    <t>F43</t>
-  </si>
-  <si>
-    <t>F44</t>
-  </si>
-  <si>
-    <t>F45</t>
-  </si>
-  <si>
-    <t>F48</t>
-  </si>
-  <si>
-    <t>F49</t>
-  </si>
-  <si>
-    <t>F50</t>
-  </si>
-  <si>
-    <t>F51</t>
-  </si>
-  <si>
-    <t>F52</t>
-  </si>
-  <si>
-    <t>F54</t>
-  </si>
-  <si>
-    <t>F55</t>
-  </si>
-  <si>
-    <t>F56</t>
-  </si>
-  <si>
-    <t>F57</t>
-  </si>
-  <si>
-    <t>F58</t>
-  </si>
-  <si>
-    <t>G5</t>
-  </si>
-  <si>
-    <t>G6</t>
-  </si>
-  <si>
-    <t>G7</t>
-  </si>
-  <si>
-    <t>G8</t>
-  </si>
-  <si>
-    <t>G9</t>
-  </si>
-  <si>
-    <t>G11</t>
-  </si>
-  <si>
-    <t>G12</t>
-  </si>
-  <si>
-    <t>G13</t>
-  </si>
-  <si>
-    <t>G14</t>
-  </si>
-  <si>
-    <t>G15</t>
-  </si>
-  <si>
-    <t>G17</t>
-  </si>
-  <si>
-    <t>G18</t>
-  </si>
-  <si>
-    <t>G19</t>
-  </si>
-  <si>
-    <t>G20</t>
-  </si>
-  <si>
-    <t>G21</t>
-  </si>
-  <si>
-    <t>G22</t>
-  </si>
-  <si>
-    <t>G23</t>
-  </si>
-  <si>
-    <t>G24</t>
-  </si>
-  <si>
-    <t>G27</t>
-  </si>
-  <si>
-    <t>G28</t>
-  </si>
-  <si>
-    <t>G29</t>
-  </si>
-  <si>
-    <t>G30</t>
-  </si>
-  <si>
-    <t>G31</t>
-  </si>
-  <si>
-    <t>G32</t>
-  </si>
-  <si>
-    <t>G34</t>
-  </si>
-  <si>
-    <t>G35</t>
-  </si>
-  <si>
-    <t>G36</t>
-  </si>
-  <si>
-    <t>G37</t>
-  </si>
-  <si>
-    <t>G38</t>
-  </si>
-  <si>
-    <t>G40</t>
-  </si>
-  <si>
-    <t>G41</t>
-  </si>
-  <si>
-    <t>G42</t>
-  </si>
-  <si>
-    <t>G43</t>
-  </si>
-  <si>
-    <t>G44</t>
-  </si>
-  <si>
-    <t>G45</t>
-  </si>
-  <si>
-    <t>G48</t>
-  </si>
-  <si>
-    <t>G49</t>
-  </si>
-  <si>
-    <t>G50</t>
-  </si>
-  <si>
-    <t>G51</t>
-  </si>
-  <si>
-    <t>G52</t>
-  </si>
-  <si>
-    <t>G54</t>
-  </si>
-  <si>
-    <t>G55</t>
-  </si>
-  <si>
-    <t>G56</t>
-  </si>
-  <si>
-    <t>G57</t>
-  </si>
-  <si>
-    <t>G58</t>
-  </si>
-  <si>
     <t>NA</t>
-  </si>
-  <si>
-    <t>F59</t>
-  </si>
-  <si>
-    <t>G59</t>
   </si>
   <si>
     <t>Title</t>
@@ -484,8 +208,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="170" formatCode="0.0E+00"/>
-    <numFmt numFmtId="172" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0E+00"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -563,9 +287,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="2"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -914,19 +638,19 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>141</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="D1" s="8">
         <v>0.1</v>
       </c>
       <c r="E1" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="F1" s="8">
         <v>0.15</v>
@@ -940,10 +664,10 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>47</v>
@@ -972,11 +696,13 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" t="s">
-        <v>93</v>
+      <c r="C5">
+        <f>F5</f>
+        <v>2.56</v>
+      </c>
+      <c r="D5">
+        <f t="shared" ref="D5:D9" si="0">G5</f>
+        <v>2.56</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
@@ -995,11 +721,13 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" t="s">
-        <v>94</v>
+      <c r="C6">
+        <f t="shared" ref="C6:C9" si="1">F6</f>
+        <v>2.7542287033381651E-3</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>2.7542287033381651E-3</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
@@ -1020,11 +748,13 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s">
-        <v>95</v>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>2.7542287033381651E-3</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>2.7542287033381651E-3</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
@@ -1045,11 +775,13 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" t="s">
-        <v>96</v>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
@@ -1068,11 +800,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" t="s">
-        <v>97</v>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>1.5171551500583661E-5</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>1.5171551500583661E-5</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -1098,11 +832,13 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" t="s">
-        <v>98</v>
+      <c r="C11">
+        <f t="shared" ref="C11:C15" si="2">F11</f>
+        <v>2.56</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ref="D11:D15" si="3">G11</f>
+        <v>2.5499999999999998</v>
       </c>
       <c r="E11" t="s">
         <v>42</v>
@@ -1121,11 +857,13 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" t="s">
-        <v>99</v>
+      <c r="C12">
+        <f t="shared" si="2"/>
+        <v>2.7542287033381651E-3</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="3"/>
+        <v>2.8183829312644522E-3</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1146,11 +884,13 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" t="s">
-        <v>100</v>
+      <c r="C13">
+        <f t="shared" si="2"/>
+        <v>2.7542287033381651E-3</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="3"/>
+        <v>2.8183829312644522E-3</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -1171,11 +911,13 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" t="s">
-        <v>101</v>
+      <c r="C14">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
@@ -1194,11 +936,13 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" t="s">
-        <v>102</v>
+      <c r="C15">
+        <f t="shared" si="2"/>
+        <v>3.7928878751459152E-5</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="3"/>
+        <v>3.9716411736214029E-5</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -1224,11 +968,13 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" t="s">
-        <v>103</v>
+      <c r="C17">
+        <f t="shared" ref="C17:C24" si="4">F17</f>
+        <v>0.52929999999999999</v>
+      </c>
+      <c r="D17">
+        <f t="shared" ref="D17:D24" si="5">G17</f>
+        <v>0.52339999999999998</v>
       </c>
       <c r="E17" t="s">
         <v>4</v>
@@ -1247,11 +993,13 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" t="s">
-        <v>104</v>
+      <c r="C18">
+        <f t="shared" si="4"/>
+        <v>4.22</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="5"/>
+        <v>4.3600000000000003</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
@@ -1270,11 +1018,13 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" t="s">
-        <v>105</v>
+      <c r="C19">
+        <f t="shared" si="4"/>
+        <v>6.0255958607435738E-5</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="5"/>
+        <v>4.3651583224016559E-5</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
@@ -1295,11 +1045,13 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" t="s">
-        <v>106</v>
+      <c r="C20">
+        <f t="shared" si="4"/>
+        <v>0.32262586858466413</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="5"/>
+        <v>0.31902962330854562</v>
       </c>
       <c r="E20" t="s">
         <v>22</v>
@@ -1320,11 +1072,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" t="s">
-        <v>107</v>
+      <c r="C21">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
       </c>
       <c r="E21" t="s">
         <v>21</v>
@@ -1343,11 +1097,13 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C22" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" t="s">
-        <v>108</v>
+      <c r="C22">
+        <f t="shared" si="4"/>
+        <v>3.8880261966251047E-5</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="5"/>
+        <v>2.7852296305559265E-5</v>
       </c>
       <c r="E22" t="s">
         <v>20</v>
@@ -1368,11 +1124,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C23" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" t="s">
-        <v>109</v>
+      <c r="C23">
+        <f t="shared" si="4"/>
+        <v>2.9120158626775136E-5</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="5"/>
+        <v>NA</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
@@ -1382,7 +1140,7 @@
         <v>2.9120158626775136E-5</v>
       </c>
       <c r="G23" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="H23" t="s">
         <v>28</v>
@@ -1392,11 +1150,13 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" t="s">
-        <v>110</v>
+      <c r="C24">
+        <f t="shared" si="4"/>
+        <v>-0.65455446743040535</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="5"/>
+        <v>NA</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -1406,7 +1166,7 @@
         <v>-0.65455446743040535</v>
       </c>
       <c r="G24" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="H24" t="s">
         <v>29</v>
@@ -1426,17 +1186,19 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C27" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" t="s">
-        <v>111</v>
+      <c r="C27" t="str">
+        <f t="shared" ref="C27:C32" si="6">F27</f>
+        <v>NA</v>
+      </c>
+      <c r="D27">
+        <f t="shared" ref="D27:D32" si="7">G27</f>
+        <v>1</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -1449,11 +1211,13 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C28" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" t="s">
-        <v>112</v>
+      <c r="C28">
+        <f t="shared" si="6"/>
+        <v>3.03</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="7"/>
+        <v>3.03</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -1472,11 +1236,13 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C29" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" t="s">
-        <v>113</v>
+      <c r="C29">
+        <f t="shared" si="6"/>
+        <v>9.3325430079699062E-4</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="7"/>
+        <v>9.3325430079699062E-4</v>
       </c>
       <c r="E29" t="s">
         <v>23</v>
@@ -1497,11 +1263,13 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C30" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" t="s">
-        <v>114</v>
+      <c r="C30">
+        <f t="shared" si="6"/>
+        <v>9.3325430079699062E-4</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="7"/>
+        <v>9.3325430079699062E-4</v>
       </c>
       <c r="E30" t="s">
         <v>30</v>
@@ -1522,11 +1290,13 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C31" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" t="s">
-        <v>115</v>
+      <c r="C31">
+        <f t="shared" si="6"/>
+        <v>0.1</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="7"/>
+        <v>0.1</v>
       </c>
       <c r="E31" t="s">
         <v>31</v>
@@ -1545,11 +1315,13 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C32" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" t="s">
-        <v>116</v>
+      <c r="C32">
+        <f t="shared" si="6"/>
+        <v>8.7096358995607971E-6</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="7"/>
+        <v>8.7096358995607971E-6</v>
       </c>
       <c r="E32" t="s">
         <v>20</v>
@@ -1575,11 +1347,13 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C34" t="s">
-        <v>72</v>
-      </c>
-      <c r="D34" t="s">
-        <v>117</v>
+      <c r="C34">
+        <f t="shared" ref="C34:C38" si="8">F34</f>
+        <v>4.04</v>
+      </c>
+      <c r="D34">
+        <f t="shared" ref="D34:D38" si="9">G34</f>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E34" t="s">
         <v>5</v>
@@ -1598,11 +1372,13 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C35" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" t="s">
-        <v>118</v>
+      <c r="C35">
+        <f t="shared" si="8"/>
+        <v>9.1201083935590923E-5</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="9"/>
+        <v>7.9432823472428153E-5</v>
       </c>
       <c r="E35" t="s">
         <v>23</v>
@@ -1623,11 +1399,13 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C36" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" t="s">
-        <v>119</v>
+      <c r="C36">
+        <f t="shared" si="8"/>
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="9"/>
+        <v>1.6666666666666666E-2</v>
       </c>
       <c r="E36" t="s">
         <v>30</v>
@@ -1648,11 +1426,13 @@
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C37" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37" t="s">
-        <v>120</v>
+      <c r="C37">
+        <f t="shared" si="8"/>
+        <v>6.666666666666668E-2</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="9"/>
+        <v>6.666666666666668E-2</v>
       </c>
       <c r="E37" t="s">
         <v>31</v>
@@ -1673,11 +1453,13 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C38" t="s">
-        <v>76</v>
-      </c>
-      <c r="D38" t="s">
-        <v>121</v>
+      <c r="C38">
+        <f t="shared" si="8"/>
+        <v>2.2800270983897727E-5</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="9"/>
+        <v>1.9858205868107035E-5</v>
       </c>
       <c r="E38" t="s">
         <v>20</v>
@@ -1703,11 +1485,13 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C40" t="s">
-        <v>77</v>
-      </c>
-      <c r="D40" t="s">
-        <v>122</v>
+      <c r="C40">
+        <f t="shared" ref="C40:C45" si="10">F40</f>
+        <v>4.54</v>
+      </c>
+      <c r="D40">
+        <f t="shared" ref="D40:D45" si="11">G40</f>
+        <v>4.6399999999999997</v>
       </c>
       <c r="E40" t="s">
         <v>16</v>
@@ -1726,11 +1510,13 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C41" t="s">
-        <v>78</v>
-      </c>
-      <c r="D41" t="s">
-        <v>123</v>
+      <c r="C41">
+        <f t="shared" si="10"/>
+        <v>2.8840315031266029E-5</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="11"/>
+        <v>2.2908676527677729E-5</v>
       </c>
       <c r="E41" t="s">
         <v>23</v>
@@ -1751,11 +1537,13 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C42" t="s">
-        <v>79</v>
-      </c>
-      <c r="D42" t="s">
-        <v>124</v>
+      <c r="C42">
+        <f t="shared" si="10"/>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="11"/>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="E42" t="s">
         <v>30</v>
@@ -1776,11 +1564,13 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C43" t="s">
-        <v>80</v>
-      </c>
-      <c r="D43" t="s">
-        <v>125</v>
+      <c r="C43">
+        <f t="shared" si="10"/>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="11"/>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="E43" t="s">
         <v>31</v>
@@ -1801,11 +1591,13 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C44" t="s">
-        <v>81</v>
-      </c>
-      <c r="D44" t="s">
-        <v>126</v>
+      <c r="C44">
+        <f t="shared" si="10"/>
+        <v>2.8840315031266033E-5</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="11"/>
+        <v>2.2908676527677729E-5</v>
       </c>
       <c r="E44" t="s">
         <v>20</v>
@@ -1826,11 +1618,13 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C45" t="s">
-        <v>82</v>
-      </c>
-      <c r="D45" t="s">
-        <v>127</v>
+      <c r="C45">
+        <f t="shared" si="10"/>
+        <v>1.8637790035011686E-5</v>
+      </c>
+      <c r="D45" t="str">
+        <f t="shared" si="11"/>
+        <v>NA</v>
       </c>
       <c r="E45" t="s">
         <v>6</v>
@@ -1840,7 +1634,7 @@
         <v>1.8637790035011686E-5</v>
       </c>
       <c r="G45" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="H45" t="s">
         <v>28</v>
@@ -1860,11 +1654,13 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C48" t="s">
-        <v>83</v>
-      </c>
-      <c r="D48" t="s">
-        <v>128</v>
+      <c r="C48">
+        <f t="shared" ref="C48:C52" si="12">F48</f>
+        <v>11.26</v>
+      </c>
+      <c r="D48">
+        <f t="shared" ref="D48:D52" si="13">G48</f>
+        <v>11.12</v>
       </c>
       <c r="E48" t="s">
         <v>18</v>
@@ -1883,11 +1679,13 @@
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C49" t="s">
-        <v>84</v>
-      </c>
-      <c r="D49" t="s">
-        <v>129</v>
+      <c r="C49">
+        <f t="shared" si="12"/>
+        <v>1.8197008586099809E-3</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="13"/>
+        <v>1.3182567385564036E-3</v>
       </c>
       <c r="E49" t="s">
         <v>32</v>
@@ -1908,11 +1706,13 @@
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C50" t="s">
-        <v>85</v>
-      </c>
-      <c r="D50" t="s">
-        <v>130</v>
+      <c r="C50">
+        <f t="shared" si="12"/>
+        <v>1.8197008586099809E-3</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="13"/>
+        <v>1.3182567385564036E-3</v>
       </c>
       <c r="E50" t="s">
         <v>33</v>
@@ -1933,11 +1733,13 @@
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C51" t="s">
-        <v>86</v>
-      </c>
-      <c r="D51" t="s">
-        <v>131</v>
+      <c r="C51">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
       </c>
       <c r="E51" t="s">
         <v>34</v>
@@ -1956,11 +1758,13 @@
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C52" t="s">
-        <v>87</v>
-      </c>
-      <c r="D52" t="s">
-        <v>132</v>
+      <c r="C52">
+        <f t="shared" si="12"/>
+        <v>6.6226224296518036E-6</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="13"/>
+        <v>3.4756016574987324E-6</v>
       </c>
       <c r="E52" t="s">
         <v>20</v>
@@ -1986,11 +1790,13 @@
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" t="s">
-        <v>133</v>
+      <c r="C54">
+        <f t="shared" ref="C54:C59" si="14">F54</f>
+        <v>10.4</v>
+      </c>
+      <c r="D54">
+        <f t="shared" ref="D54:D59" si="15">G54</f>
+        <v>10.4</v>
       </c>
       <c r="E54" t="s">
         <v>5</v>
@@ -2009,11 +1815,13 @@
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C55" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" t="s">
-        <v>134</v>
+      <c r="C55">
+        <f t="shared" si="14"/>
+        <v>2.5118864315095817E-4</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="15"/>
+        <v>2.5118864315095817E-4</v>
       </c>
       <c r="E55" t="s">
         <v>32</v>
@@ -2034,11 +1842,13 @@
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C56" t="s">
-        <v>90</v>
-      </c>
-      <c r="D56" t="s">
-        <v>135</v>
+      <c r="C56">
+        <f t="shared" si="14"/>
+        <v>0.02</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="15"/>
+        <v>0.02</v>
       </c>
       <c r="E56" t="s">
         <v>33</v>
@@ -2059,11 +1869,13 @@
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C57" t="s">
-        <v>91</v>
-      </c>
-      <c r="D57" t="s">
-        <v>136</v>
+      <c r="C57">
+        <f t="shared" si="14"/>
+        <v>0.37999999999999995</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="15"/>
+        <v>0.37999999999999995</v>
       </c>
       <c r="E57" t="s">
         <v>34</v>
@@ -2084,11 +1896,13 @@
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C58" t="s">
-        <v>92</v>
-      </c>
-      <c r="D58" t="s">
-        <v>137</v>
+      <c r="C58">
+        <f t="shared" si="14"/>
+        <v>1.3220454902682011E-5</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="15"/>
+        <v>1.3220454902682011E-5</v>
       </c>
       <c r="E58" t="s">
         <v>20</v>
@@ -2109,11 +1923,13 @@
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C59" t="s">
-        <v>139</v>
-      </c>
-      <c r="D59" t="s">
-        <v>140</v>
+      <c r="C59">
+        <f t="shared" si="14"/>
+        <v>9.1347834731286396E-6</v>
+      </c>
+      <c r="D59" t="str">
+        <f t="shared" si="15"/>
+        <v>NA</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
@@ -2123,7 +1939,7 @@
         <v>9.1347834731286396E-6</v>
       </c>
       <c r="G59" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="H59" t="s">
         <v>28</v>
